--- a/spice-auction-pwa/backend/data/SOURCE.xlsx
+++ b/spice-auction-pwa/backend/data/SOURCE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4512" uniqueCount="2275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="2278">
   <si>
     <t>NAME</t>
   </si>
@@ -4105,7 +4105,7 @@
     <t>8838618302</t>
   </si>
   <si>
-    <t>11227657026</t>
+    <t>112276570262</t>
   </si>
   <si>
     <t>KALAIARASAN.M</t>
@@ -6836,6 +6836,15 @@
   </si>
   <si>
     <t>1234567890654</t>
+  </si>
+  <si>
+    <t>PRIYA</t>
+  </si>
+  <si>
+    <t>0987663728</t>
+  </si>
+  <si>
+    <t>10,salai</t>
   </si>
 </sst>
 </file>
@@ -7216,7 +7225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L376"/>
+  <dimension ref="A1:L377"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -21520,6 +21529,44 @@
         <v>2274</v>
       </c>
     </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B377" t="s">
+        <v>2244</v>
+      </c>
+      <c r="C377" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D377" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E377" t="s">
+        <v>16</v>
+      </c>
+      <c r="F377" t="s">
+        <v>2277</v>
+      </c>
+      <c r="G377" t="s">
+        <v>2247</v>
+      </c>
+      <c r="H377" t="s">
+        <v>2248</v>
+      </c>
+      <c r="I377" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J377" t="s">
+        <v>32</v>
+      </c>
+      <c r="K377" t="s">
+        <v>1680</v>
+      </c>
+      <c r="L377" t="s">
+        <v>1748</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/spice-auction-pwa/backend/data/SOURCE.xlsx
+++ b/spice-auction-pwa/backend/data/SOURCE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="2278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="2277">
   <si>
     <t>NAME</t>
   </si>
@@ -4649,9 +4649,6 @@
   </si>
   <si>
     <t>PATHUMURY</t>
-  </si>
-  <si>
-    <t>1132155000087066</t>
   </si>
   <si>
     <t>MANU MANOHARAN</t>
@@ -16165,30 +16162,30 @@
         <v>21</v>
       </c>
       <c r="K235" t="s">
-        <v>867</v>
+        <v>16</v>
       </c>
       <c r="L235" t="s">
-        <v>1546</v>
+        <v>16</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B236" t="s">
         <v>1401</v>
       </c>
       <c r="C236" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D236" t="s">
         <v>1548</v>
       </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
+        <v>16</v>
+      </c>
+      <c r="F236" t="s">
         <v>1549</v>
-      </c>
-      <c r="E236" t="s">
-        <v>16</v>
-      </c>
-      <c r="F236" t="s">
-        <v>1550</v>
       </c>
       <c r="G236" t="s">
         <v>738</v>
@@ -16203,33 +16200,33 @@
         <v>21</v>
       </c>
       <c r="K236" t="s">
+        <v>1550</v>
+      </c>
+      <c r="L236" t="s">
         <v>1551</v>
-      </c>
-      <c r="L236" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B237" t="s">
         <v>1553</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C237" t="s">
         <v>1554</v>
       </c>
-      <c r="C237" t="s">
+      <c r="D237" t="s">
         <v>1555</v>
       </c>
-      <c r="D237" t="s">
+      <c r="E237" t="s">
+        <v>16</v>
+      </c>
+      <c r="F237" t="s">
         <v>1556</v>
       </c>
-      <c r="E237" t="s">
-        <v>16</v>
-      </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
         <v>1557</v>
-      </c>
-      <c r="G237" t="s">
-        <v>1558</v>
       </c>
       <c r="H237" t="s">
         <v>19</v>
@@ -16244,27 +16241,27 @@
         <v>505</v>
       </c>
       <c r="L237" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B238" t="s">
         <v>1401</v>
       </c>
       <c r="C238" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D238" t="s">
         <v>1561</v>
       </c>
-      <c r="D238" t="s">
+      <c r="E238" t="s">
+        <v>16</v>
+      </c>
+      <c r="F238" t="s">
         <v>1562</v>
-      </c>
-      <c r="E238" t="s">
-        <v>16</v>
-      </c>
-      <c r="F238" t="s">
-        <v>1563</v>
       </c>
       <c r="G238" t="s">
         <v>1457</v>
@@ -16282,27 +16279,27 @@
         <v>298</v>
       </c>
       <c r="L238" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B239" t="s">
         <v>1401</v>
       </c>
       <c r="C239" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D239" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E239" t="s">
+        <v>16</v>
+      </c>
+      <c r="F239" t="s">
         <v>1562</v>
-      </c>
-      <c r="E239" t="s">
-        <v>16</v>
-      </c>
-      <c r="F239" t="s">
-        <v>1563</v>
       </c>
       <c r="G239" t="s">
         <v>1457</v>
@@ -16320,30 +16317,30 @@
         <v>298</v>
       </c>
       <c r="L239" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B240" t="s">
         <v>1401</v>
       </c>
       <c r="C240" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D240" t="s">
         <v>1569</v>
       </c>
-      <c r="D240" t="s">
+      <c r="E240" t="s">
+        <v>16</v>
+      </c>
+      <c r="F240" t="s">
         <v>1570</v>
       </c>
-      <c r="E240" t="s">
-        <v>16</v>
-      </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>1571</v>
-      </c>
-      <c r="G240" t="s">
-        <v>1572</v>
       </c>
       <c r="H240" t="s">
         <v>169</v>
@@ -16358,27 +16355,27 @@
         <v>595</v>
       </c>
       <c r="L240" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B241" t="s">
         <v>1401</v>
       </c>
       <c r="C241" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D241" t="s">
         <v>1575</v>
       </c>
-      <c r="D241" t="s">
+      <c r="E241" t="s">
+        <v>16</v>
+      </c>
+      <c r="F241" t="s">
         <v>1576</v>
-      </c>
-      <c r="E241" t="s">
-        <v>16</v>
-      </c>
-      <c r="F241" t="s">
-        <v>1577</v>
       </c>
       <c r="G241" t="s">
         <v>1457</v>
@@ -16393,30 +16390,30 @@
         <v>21</v>
       </c>
       <c r="K241" t="s">
+        <v>1577</v>
+      </c>
+      <c r="L241" t="s">
         <v>1578</v>
-      </c>
-      <c r="L241" t="s">
-        <v>1579</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B242" t="s">
         <v>1580</v>
       </c>
-      <c r="B242" t="s">
+      <c r="C242" t="s">
         <v>1581</v>
       </c>
-      <c r="C242" t="s">
+      <c r="D242" t="s">
         <v>1582</v>
       </c>
-      <c r="D242" t="s">
+      <c r="E242" t="s">
+        <v>16</v>
+      </c>
+      <c r="F242" t="s">
         <v>1583</v>
-      </c>
-      <c r="E242" t="s">
-        <v>16</v>
-      </c>
-      <c r="F242" t="s">
-        <v>1584</v>
       </c>
       <c r="G242" t="s">
         <v>1457</v>
@@ -16434,18 +16431,18 @@
         <v>1358</v>
       </c>
       <c r="L242" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B243" t="s">
         <v>1586</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C243" t="s">
         <v>1587</v>
-      </c>
-      <c r="C243" t="s">
-        <v>1588</v>
       </c>
       <c r="D243" t="s">
         <v>1065</v>
@@ -16454,10 +16451,10 @@
         <v>16</v>
       </c>
       <c r="F243" t="s">
+        <v>1588</v>
+      </c>
+      <c r="G243" t="s">
         <v>1589</v>
-      </c>
-      <c r="G243" t="s">
-        <v>1590</v>
       </c>
       <c r="H243" t="s">
         <v>41</v>
@@ -16472,27 +16469,27 @@
         <v>193</v>
       </c>
       <c r="L243" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B244" t="s">
         <v>1592</v>
       </c>
-      <c r="B244" t="s">
+      <c r="C244" t="s">
         <v>1593</v>
       </c>
-      <c r="C244" t="s">
+      <c r="D244" t="s">
         <v>1594</v>
       </c>
-      <c r="D244" t="s">
+      <c r="E244" t="s">
+        <v>16</v>
+      </c>
+      <c r="F244" t="s">
         <v>1595</v>
-      </c>
-      <c r="E244" t="s">
-        <v>16</v>
-      </c>
-      <c r="F244" t="s">
-        <v>1596</v>
       </c>
       <c r="G244" t="s">
         <v>1357</v>
@@ -16507,30 +16504,30 @@
         <v>21</v>
       </c>
       <c r="K244" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L244" t="s">
         <v>1597</v>
-      </c>
-      <c r="L244" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B245" t="s">
         <v>1599</v>
       </c>
-      <c r="B245" t="s">
+      <c r="C245" t="s">
         <v>1600</v>
       </c>
-      <c r="C245" t="s">
+      <c r="D245" t="s">
         <v>1601</v>
       </c>
-      <c r="D245" t="s">
+      <c r="E245" t="s">
+        <v>16</v>
+      </c>
+      <c r="F245" t="s">
         <v>1602</v>
-      </c>
-      <c r="E245" t="s">
-        <v>16</v>
-      </c>
-      <c r="F245" t="s">
-        <v>1603</v>
       </c>
       <c r="G245" t="s">
         <v>416</v>
@@ -16545,21 +16542,21 @@
         <v>21</v>
       </c>
       <c r="K245" t="s">
+        <v>1603</v>
+      </c>
+      <c r="L245" t="s">
         <v>1604</v>
-      </c>
-      <c r="L245" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B246" t="s">
         <v>1401</v>
       </c>
       <c r="C246" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D246" t="s">
         <v>1085</v>
@@ -16568,7 +16565,7 @@
         <v>16</v>
       </c>
       <c r="F246" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G246" t="s">
         <v>89</v>
@@ -16586,27 +16583,27 @@
         <v>107</v>
       </c>
       <c r="L246" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B247" t="s">
         <v>1610</v>
       </c>
-      <c r="B247" t="s">
+      <c r="C247" t="s">
         <v>1611</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
         <v>1612</v>
       </c>
-      <c r="D247" t="s">
+      <c r="E247" t="s">
+        <v>16</v>
+      </c>
+      <c r="F247" t="s">
         <v>1613</v>
-      </c>
-      <c r="E247" t="s">
-        <v>16</v>
-      </c>
-      <c r="F247" t="s">
-        <v>1614</v>
       </c>
       <c r="G247" t="s">
         <v>541</v>
@@ -16624,18 +16621,18 @@
         <v>50</v>
       </c>
       <c r="L247" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B248" t="s">
         <v>1401</v>
       </c>
       <c r="C248" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D248" t="s">
         <v>213</v>
@@ -16644,10 +16641,10 @@
         <v>16</v>
       </c>
       <c r="F248" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G248" t="s">
         <v>1618</v>
-      </c>
-      <c r="G248" t="s">
-        <v>1619</v>
       </c>
       <c r="H248" t="s">
         <v>169</v>
@@ -16662,30 +16659,30 @@
         <v>170</v>
       </c>
       <c r="L248" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B249" t="s">
         <v>1621</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C249" t="s">
         <v>1622</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D249" t="s">
         <v>1623</v>
       </c>
-      <c r="D249" t="s">
+      <c r="E249" t="s">
+        <v>16</v>
+      </c>
+      <c r="F249" t="s">
         <v>1624</v>
       </c>
-      <c r="E249" t="s">
-        <v>16</v>
-      </c>
-      <c r="F249" t="s">
+      <c r="G249" t="s">
         <v>1625</v>
-      </c>
-      <c r="G249" t="s">
-        <v>1626</v>
       </c>
       <c r="H249" t="s">
         <v>41</v>
@@ -16697,30 +16694,30 @@
         <v>21</v>
       </c>
       <c r="K249" t="s">
+        <v>1626</v>
+      </c>
+      <c r="L249" t="s">
         <v>1627</v>
-      </c>
-      <c r="L249" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B250" t="s">
         <v>1401</v>
       </c>
       <c r="C250" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D250" t="s">
         <v>1630</v>
       </c>
-      <c r="D250" t="s">
+      <c r="E250" t="s">
+        <v>16</v>
+      </c>
+      <c r="F250" t="s">
         <v>1631</v>
-      </c>
-      <c r="E250" t="s">
-        <v>16</v>
-      </c>
-      <c r="F250" t="s">
-        <v>1632</v>
       </c>
       <c r="G250" t="s">
         <v>1457</v>
@@ -16738,21 +16735,21 @@
         <v>854</v>
       </c>
       <c r="L250" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B251" t="s">
         <v>1401</v>
       </c>
       <c r="C251" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D251" t="s">
         <v>1635</v>
-      </c>
-      <c r="D251" t="s">
-        <v>1636</v>
       </c>
       <c r="E251" t="s">
         <v>16</v>
@@ -16776,30 +16773,30 @@
         <v>170</v>
       </c>
       <c r="L251" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B252" t="s">
         <v>1401</v>
       </c>
       <c r="C252" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D252" t="s">
         <v>1639</v>
       </c>
-      <c r="D252" t="s">
+      <c r="E252" t="s">
+        <v>16</v>
+      </c>
+      <c r="F252" t="s">
         <v>1640</v>
       </c>
-      <c r="E252" t="s">
-        <v>16</v>
-      </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
         <v>1641</v>
-      </c>
-      <c r="G252" t="s">
-        <v>1642</v>
       </c>
       <c r="H252" t="s">
         <v>253</v>
@@ -16814,27 +16811,27 @@
         <v>1390</v>
       </c>
       <c r="L252" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B253" t="s">
         <v>1644</v>
       </c>
-      <c r="B253" t="s">
+      <c r="C253" t="s">
         <v>1645</v>
       </c>
-      <c r="C253" t="s">
+      <c r="D253" t="s">
         <v>1646</v>
       </c>
-      <c r="D253" t="s">
+      <c r="E253" t="s">
+        <v>16</v>
+      </c>
+      <c r="F253" t="s">
         <v>1647</v>
-      </c>
-      <c r="E253" t="s">
-        <v>16</v>
-      </c>
-      <c r="F253" t="s">
-        <v>1648</v>
       </c>
       <c r="G253" t="s">
         <v>49</v>
@@ -16849,21 +16846,21 @@
         <v>21</v>
       </c>
       <c r="K253" t="s">
+        <v>1648</v>
+      </c>
+      <c r="L253" t="s">
         <v>1649</v>
-      </c>
-      <c r="L253" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="B254" t="s">
         <v>1401</v>
       </c>
       <c r="C254" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="D254" t="s">
         <v>383</v>
@@ -16872,7 +16869,7 @@
         <v>16</v>
       </c>
       <c r="F254" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="G254" t="s">
         <v>215</v>
@@ -16887,33 +16884,33 @@
         <v>21</v>
       </c>
       <c r="K254" t="s">
+        <v>1653</v>
+      </c>
+      <c r="L254" t="s">
         <v>1654</v>
-      </c>
-      <c r="L254" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="B255" t="s">
         <v>1401</v>
       </c>
       <c r="C255" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D255" t="s">
         <v>1657</v>
       </c>
-      <c r="D255" t="s">
-        <v>1658</v>
-      </c>
       <c r="E255" t="s">
         <v>16</v>
       </c>
       <c r="F255" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G255" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H255" t="s">
         <v>169</v>
@@ -16928,30 +16925,30 @@
         <v>854</v>
       </c>
       <c r="L255" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="B256" t="s">
         <v>1401</v>
       </c>
       <c r="C256" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D256" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="E256" t="s">
         <v>16</v>
       </c>
       <c r="F256" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G256" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H256" t="s">
         <v>169</v>
@@ -16966,27 +16963,27 @@
         <v>254</v>
       </c>
       <c r="L256" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B257" t="s">
         <v>1401</v>
       </c>
       <c r="C257" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E257" t="s">
+        <v>16</v>
+      </c>
+      <c r="F257" t="s">
         <v>1664</v>
-      </c>
-      <c r="D257" t="s">
-        <v>1636</v>
-      </c>
-      <c r="E257" t="s">
-        <v>16</v>
-      </c>
-      <c r="F257" t="s">
-        <v>1665</v>
       </c>
       <c r="G257" t="s">
         <v>215</v>
@@ -17004,27 +17001,27 @@
         <v>170</v>
       </c>
       <c r="L257" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B258" t="s">
         <v>1401</v>
       </c>
       <c r="C258" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D258" t="s">
         <v>1668</v>
       </c>
-      <c r="D258" t="s">
+      <c r="E258" t="s">
+        <v>16</v>
+      </c>
+      <c r="F258" t="s">
         <v>1669</v>
-      </c>
-      <c r="E258" t="s">
-        <v>16</v>
-      </c>
-      <c r="F258" t="s">
-        <v>1670</v>
       </c>
       <c r="G258" t="s">
         <v>1457</v>
@@ -17039,21 +17036,21 @@
         <v>21</v>
       </c>
       <c r="K258" t="s">
+        <v>1670</v>
+      </c>
+      <c r="L258" t="s">
         <v>1671</v>
-      </c>
-      <c r="L258" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B259" t="s">
         <v>1401</v>
       </c>
       <c r="C259" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="D259" t="s">
         <v>621</v>
@@ -17062,10 +17059,10 @@
         <v>16</v>
       </c>
       <c r="F259" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="G259" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H259" t="s">
         <v>41</v>
@@ -17077,21 +17074,21 @@
         <v>21</v>
       </c>
       <c r="K259" t="s">
+        <v>1675</v>
+      </c>
+      <c r="L259" t="s">
         <v>1676</v>
-      </c>
-      <c r="L259" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="B260" t="s">
         <v>1401</v>
       </c>
       <c r="C260" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="D260" t="s">
         <v>1221</v>
@@ -17100,10 +17097,10 @@
         <v>16</v>
       </c>
       <c r="F260" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G260" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H260" t="s">
         <v>169</v>
@@ -17115,21 +17112,21 @@
         <v>21</v>
       </c>
       <c r="K260" t="s">
+        <v>1679</v>
+      </c>
+      <c r="L260" t="s">
         <v>1680</v>
-      </c>
-      <c r="L260" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B261" t="s">
         <v>1401</v>
       </c>
       <c r="C261" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="D261" t="s">
         <v>1221</v>
@@ -17156,27 +17153,27 @@
         <v>1390</v>
       </c>
       <c r="L261" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B262" t="s">
         <v>1401</v>
       </c>
       <c r="C262" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D262" t="s">
         <v>1686</v>
       </c>
-      <c r="D262" t="s">
+      <c r="E262" t="s">
+        <v>16</v>
+      </c>
+      <c r="F262" t="s">
         <v>1687</v>
-      </c>
-      <c r="E262" t="s">
-        <v>16</v>
-      </c>
-      <c r="F262" t="s">
-        <v>1688</v>
       </c>
       <c r="G262" t="s">
         <v>215</v>
@@ -17194,27 +17191,27 @@
         <v>854</v>
       </c>
       <c r="L262" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="B263" t="s">
         <v>1401</v>
       </c>
       <c r="C263" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="D263" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E263" t="s">
+        <v>16</v>
+      </c>
+      <c r="F263" t="s">
         <v>1687</v>
-      </c>
-      <c r="E263" t="s">
-        <v>16</v>
-      </c>
-      <c r="F263" t="s">
-        <v>1688</v>
       </c>
       <c r="G263" t="s">
         <v>215</v>
@@ -17232,18 +17229,18 @@
         <v>42</v>
       </c>
       <c r="L263" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B264" t="s">
         <v>1401</v>
       </c>
       <c r="C264" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="D264" t="s">
         <v>1221</v>
@@ -17252,10 +17249,10 @@
         <v>16</v>
       </c>
       <c r="F264" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="G264" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H264" t="s">
         <v>169</v>
@@ -17270,18 +17267,18 @@
         <v>1390</v>
       </c>
       <c r="L264" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B265" t="s">
         <v>1401</v>
       </c>
       <c r="C265" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="D265" t="s">
         <v>899</v>
@@ -17305,21 +17302,21 @@
         <v>21</v>
       </c>
       <c r="K265" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="L265" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="B266" t="s">
         <v>1401</v>
       </c>
       <c r="C266" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="D266" t="s">
         <v>539</v>
@@ -17328,7 +17325,7 @@
         <v>16</v>
       </c>
       <c r="F266" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="G266" t="s">
         <v>89</v>
@@ -17343,30 +17340,30 @@
         <v>21</v>
       </c>
       <c r="K266" t="s">
+        <v>1701</v>
+      </c>
+      <c r="L266" t="s">
         <v>1702</v>
-      </c>
-      <c r="L266" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C267" t="s">
         <v>1704</v>
       </c>
-      <c r="B267" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C267" t="s">
+      <c r="D267" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E267" t="s">
+        <v>16</v>
+      </c>
+      <c r="F267" t="s">
         <v>1705</v>
-      </c>
-      <c r="D267" t="s">
-        <v>1647</v>
-      </c>
-      <c r="E267" t="s">
-        <v>16</v>
-      </c>
-      <c r="F267" t="s">
-        <v>1706</v>
       </c>
       <c r="G267" t="s">
         <v>49</v>
@@ -17381,33 +17378,33 @@
         <v>21</v>
       </c>
       <c r="K267" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L267" t="s">
         <v>1707</v>
-      </c>
-      <c r="L267" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="B268" t="s">
         <v>1401</v>
       </c>
       <c r="C268" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D268" t="s">
         <v>1710</v>
       </c>
-      <c r="D268" t="s">
+      <c r="E268" t="s">
+        <v>16</v>
+      </c>
+      <c r="F268" t="s">
         <v>1711</v>
       </c>
-      <c r="E268" t="s">
-        <v>16</v>
-      </c>
-      <c r="F268" t="s">
+      <c r="G268" t="s">
         <v>1712</v>
-      </c>
-      <c r="G268" t="s">
-        <v>1713</v>
       </c>
       <c r="H268" t="s">
         <v>245</v>
@@ -17422,27 +17419,27 @@
         <v>208</v>
       </c>
       <c r="L268" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B269" t="s">
         <v>1401</v>
       </c>
       <c r="C269" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D269" t="s">
         <v>1716</v>
       </c>
-      <c r="D269" t="s">
+      <c r="E269" t="s">
+        <v>16</v>
+      </c>
+      <c r="F269" t="s">
         <v>1717</v>
-      </c>
-      <c r="E269" t="s">
-        <v>16</v>
-      </c>
-      <c r="F269" t="s">
-        <v>1718</v>
       </c>
       <c r="G269" t="s">
         <v>429</v>
@@ -17457,30 +17454,30 @@
         <v>21</v>
       </c>
       <c r="K269" t="s">
+        <v>1718</v>
+      </c>
+      <c r="L269" t="s">
         <v>1719</v>
-      </c>
-      <c r="L269" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B270" t="s">
         <v>1401</v>
       </c>
       <c r="C270" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D270" t="s">
         <v>1722</v>
       </c>
-      <c r="D270" t="s">
+      <c r="E270" t="s">
+        <v>16</v>
+      </c>
+      <c r="F270" t="s">
         <v>1723</v>
-      </c>
-      <c r="E270" t="s">
-        <v>16</v>
-      </c>
-      <c r="F270" t="s">
-        <v>1724</v>
       </c>
       <c r="G270" t="s">
         <v>252</v>
@@ -17498,27 +17495,27 @@
         <v>854</v>
       </c>
       <c r="L270" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B271" t="s">
         <v>1401</v>
       </c>
       <c r="C271" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D271" t="s">
         <v>1727</v>
       </c>
-      <c r="D271" t="s">
-        <v>1728</v>
-      </c>
       <c r="E271" t="s">
         <v>16</v>
       </c>
       <c r="F271" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G271" t="s">
         <v>429</v>
@@ -17536,27 +17533,27 @@
         <v>854</v>
       </c>
       <c r="L271" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B272" t="s">
         <v>1401</v>
       </c>
       <c r="C272" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D272" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E272" t="s">
+        <v>16</v>
+      </c>
+      <c r="F272" t="s">
         <v>1731</v>
-      </c>
-      <c r="D272" t="s">
-        <v>1728</v>
-      </c>
-      <c r="E272" t="s">
-        <v>16</v>
-      </c>
-      <c r="F272" t="s">
-        <v>1732</v>
       </c>
       <c r="G272" t="s">
         <v>1410</v>
@@ -17574,21 +17571,21 @@
         <v>595</v>
       </c>
       <c r="L272" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B273" t="s">
         <v>1401</v>
       </c>
       <c r="C273" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="D273" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="E273" t="s">
         <v>16</v>
@@ -17612,30 +17609,30 @@
         <v>1390</v>
       </c>
       <c r="L273" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B274" t="s">
         <v>1401</v>
       </c>
       <c r="C274" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D274" t="s">
         <v>1738</v>
       </c>
-      <c r="D274" t="s">
+      <c r="E274" t="s">
+        <v>16</v>
+      </c>
+      <c r="F274" t="s">
         <v>1739</v>
       </c>
-      <c r="E274" t="s">
-        <v>16</v>
-      </c>
-      <c r="F274" t="s">
+      <c r="G274" t="s">
         <v>1740</v>
-      </c>
-      <c r="G274" t="s">
-        <v>1741</v>
       </c>
       <c r="H274" t="s">
         <v>262</v>
@@ -17650,27 +17647,27 @@
         <v>854</v>
       </c>
       <c r="L274" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B275" t="s">
         <v>1401</v>
       </c>
       <c r="C275" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D275" t="s">
         <v>1744</v>
       </c>
-      <c r="D275" t="s">
+      <c r="E275" t="s">
+        <v>16</v>
+      </c>
+      <c r="F275" t="s">
         <v>1745</v>
-      </c>
-      <c r="E275" t="s">
-        <v>16</v>
-      </c>
-      <c r="F275" t="s">
-        <v>1746</v>
       </c>
       <c r="G275" t="s">
         <v>1397</v>
@@ -17685,30 +17682,30 @@
         <v>21</v>
       </c>
       <c r="K275" t="s">
+        <v>1746</v>
+      </c>
+      <c r="L275" t="s">
         <v>1747</v>
-      </c>
-      <c r="L275" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B276" t="s">
         <v>1401</v>
       </c>
       <c r="C276" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D276" t="s">
         <v>1750</v>
       </c>
-      <c r="D276" t="s">
-        <v>1751</v>
-      </c>
       <c r="E276" t="s">
         <v>16</v>
       </c>
       <c r="F276" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="G276" t="s">
         <v>49</v>
@@ -17723,30 +17720,30 @@
         <v>21</v>
       </c>
       <c r="K276" t="s">
+        <v>1751</v>
+      </c>
+      <c r="L276" t="s">
         <v>1752</v>
-      </c>
-      <c r="L276" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B277" t="s">
         <v>1401</v>
       </c>
       <c r="C277" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D277" t="s">
         <v>1755</v>
       </c>
-      <c r="D277" t="s">
+      <c r="E277" t="s">
+        <v>16</v>
+      </c>
+      <c r="F277" t="s">
         <v>1756</v>
-      </c>
-      <c r="E277" t="s">
-        <v>16</v>
-      </c>
-      <c r="F277" t="s">
-        <v>1757</v>
       </c>
       <c r="G277" t="s">
         <v>49</v>
@@ -17761,30 +17758,30 @@
         <v>21</v>
       </c>
       <c r="K277" t="s">
+        <v>1757</v>
+      </c>
+      <c r="L277" t="s">
         <v>1758</v>
-      </c>
-      <c r="L277" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B278" t="s">
         <v>1760</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C278" t="s">
         <v>1761</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
         <v>1762</v>
       </c>
-      <c r="D278" t="s">
+      <c r="E278" t="s">
+        <v>16</v>
+      </c>
+      <c r="F278" t="s">
         <v>1763</v>
-      </c>
-      <c r="E278" t="s">
-        <v>16</v>
-      </c>
-      <c r="F278" t="s">
-        <v>1764</v>
       </c>
       <c r="G278" t="s">
         <v>1357</v>
@@ -17802,30 +17799,30 @@
         <v>1358</v>
       </c>
       <c r="L278" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B279" t="s">
         <v>1766</v>
       </c>
-      <c r="B279" t="s">
+      <c r="C279" t="s">
         <v>1767</v>
       </c>
-      <c r="C279" t="s">
+      <c r="D279" t="s">
         <v>1768</v>
       </c>
-      <c r="D279" t="s">
+      <c r="E279" t="s">
+        <v>16</v>
+      </c>
+      <c r="F279" t="s">
         <v>1769</v>
       </c>
-      <c r="E279" t="s">
-        <v>16</v>
-      </c>
-      <c r="F279" t="s">
+      <c r="G279" t="s">
         <v>1770</v>
-      </c>
-      <c r="G279" t="s">
-        <v>1771</v>
       </c>
       <c r="H279" t="s">
         <v>160</v>
@@ -17840,27 +17837,27 @@
         <v>1390</v>
       </c>
       <c r="L279" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="B280" t="s">
         <v>1386</v>
       </c>
       <c r="C280" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D280" t="s">
         <v>1774</v>
       </c>
-      <c r="D280" t="s">
+      <c r="E280" t="s">
+        <v>16</v>
+      </c>
+      <c r="F280" t="s">
         <v>1775</v>
-      </c>
-      <c r="E280" t="s">
-        <v>16</v>
-      </c>
-      <c r="F280" t="s">
-        <v>1776</v>
       </c>
       <c r="G280" t="s">
         <v>1357</v>
@@ -17878,30 +17875,30 @@
         <v>1240</v>
       </c>
       <c r="L280" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B281" t="s">
         <v>1401</v>
       </c>
       <c r="C281" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D281" t="s">
         <v>1779</v>
       </c>
-      <c r="D281" t="s">
+      <c r="E281" t="s">
+        <v>16</v>
+      </c>
+      <c r="F281" t="s">
         <v>1780</v>
       </c>
-      <c r="E281" t="s">
-        <v>16</v>
-      </c>
-      <c r="F281" t="s">
+      <c r="G281" t="s">
         <v>1781</v>
-      </c>
-      <c r="G281" t="s">
-        <v>1782</v>
       </c>
       <c r="H281" t="s">
         <v>1426</v>
@@ -17916,21 +17913,21 @@
         <v>298</v>
       </c>
       <c r="L281" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B282" t="s">
         <v>1784</v>
       </c>
-      <c r="B282" t="s">
+      <c r="C282" t="s">
         <v>1785</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
         <v>1786</v>
-      </c>
-      <c r="D282" t="s">
-        <v>1787</v>
       </c>
       <c r="E282" t="s">
         <v>16</v>
@@ -17939,7 +17936,7 @@
         <v>1396</v>
       </c>
       <c r="G282" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H282" t="s">
         <v>253</v>
@@ -17954,21 +17951,21 @@
         <v>518</v>
       </c>
       <c r="L282" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B283" t="s">
         <v>1790</v>
       </c>
-      <c r="B283" t="s">
+      <c r="C283" t="s">
         <v>1791</v>
       </c>
-      <c r="C283" t="s">
+      <c r="D283" t="s">
         <v>1792</v>
-      </c>
-      <c r="D283" t="s">
-        <v>1793</v>
       </c>
       <c r="E283" t="s">
         <v>16</v>
@@ -17992,30 +17989,30 @@
         <v>1358</v>
       </c>
       <c r="L283" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B284" t="s">
         <v>1795</v>
       </c>
-      <c r="B284" t="s">
+      <c r="C284" t="s">
         <v>1796</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
         <v>1797</v>
       </c>
-      <c r="D284" t="s">
+      <c r="E284" t="s">
+        <v>16</v>
+      </c>
+      <c r="F284" t="s">
         <v>1798</v>
       </c>
-      <c r="E284" t="s">
-        <v>16</v>
-      </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
         <v>1799</v>
-      </c>
-      <c r="G284" t="s">
-        <v>1800</v>
       </c>
       <c r="H284" t="s">
         <v>253</v>
@@ -18027,33 +18024,33 @@
         <v>21</v>
       </c>
       <c r="K284" t="s">
+        <v>1800</v>
+      </c>
+      <c r="L284" t="s">
         <v>1801</v>
-      </c>
-      <c r="L284" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C285" t="s">
         <v>1803</v>
       </c>
-      <c r="B285" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C285" t="s">
-        <v>1804</v>
-      </c>
       <c r="D285" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="E285" t="s">
         <v>16</v>
       </c>
       <c r="F285" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="G285" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H285" t="s">
         <v>253</v>
@@ -18068,30 +18065,30 @@
         <v>1240</v>
       </c>
       <c r="L285" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B286" t="s">
         <v>1806</v>
       </c>
-      <c r="B286" t="s">
+      <c r="C286" t="s">
         <v>1807</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
         <v>1808</v>
       </c>
-      <c r="D286" t="s">
+      <c r="E286" t="s">
+        <v>16</v>
+      </c>
+      <c r="F286" t="s">
         <v>1809</v>
       </c>
-      <c r="E286" t="s">
-        <v>16</v>
-      </c>
-      <c r="F286" t="s">
+      <c r="G286" t="s">
         <v>1810</v>
-      </c>
-      <c r="G286" t="s">
-        <v>1811</v>
       </c>
       <c r="H286" t="s">
         <v>236</v>
@@ -18106,30 +18103,30 @@
         <v>809</v>
       </c>
       <c r="L286" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B287" t="s">
         <v>1813</v>
       </c>
-      <c r="B287" t="s">
+      <c r="C287" t="s">
         <v>1814</v>
       </c>
-      <c r="C287" t="s">
+      <c r="D287" t="s">
         <v>1815</v>
       </c>
-      <c r="D287" t="s">
+      <c r="E287" t="s">
+        <v>16</v>
+      </c>
+      <c r="F287" t="s">
         <v>1816</v>
       </c>
-      <c r="E287" t="s">
-        <v>16</v>
-      </c>
-      <c r="F287" t="s">
-        <v>1817</v>
-      </c>
       <c r="G287" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H287" t="s">
         <v>169</v>
@@ -18144,30 +18141,30 @@
         <v>1390</v>
       </c>
       <c r="L287" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B288" t="s">
         <v>1819</v>
       </c>
-      <c r="B288" t="s">
+      <c r="C288" t="s">
         <v>1820</v>
       </c>
-      <c r="C288" t="s">
+      <c r="D288" t="s">
         <v>1821</v>
       </c>
-      <c r="D288" t="s">
+      <c r="E288" t="s">
+        <v>16</v>
+      </c>
+      <c r="F288" t="s">
         <v>1822</v>
       </c>
-      <c r="E288" t="s">
-        <v>16</v>
-      </c>
-      <c r="F288" t="s">
+      <c r="G288" t="s">
         <v>1823</v>
-      </c>
-      <c r="G288" t="s">
-        <v>1824</v>
       </c>
       <c r="H288" t="s">
         <v>1426</v>
@@ -18182,30 +18179,30 @@
         <v>1358</v>
       </c>
       <c r="L288" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B289" t="s">
         <v>1401</v>
       </c>
       <c r="C289" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D289" t="s">
         <v>1827</v>
       </c>
-      <c r="D289" t="s">
+      <c r="E289" t="s">
+        <v>16</v>
+      </c>
+      <c r="F289" t="s">
         <v>1828</v>
       </c>
-      <c r="E289" t="s">
-        <v>16</v>
-      </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
         <v>1829</v>
-      </c>
-      <c r="G289" t="s">
-        <v>1830</v>
       </c>
       <c r="H289" t="s">
         <v>169</v>
@@ -18217,30 +18214,30 @@
         <v>21</v>
       </c>
       <c r="K289" t="s">
+        <v>1830</v>
+      </c>
+      <c r="L289" t="s">
         <v>1831</v>
-      </c>
-      <c r="L289" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B290" t="s">
         <v>1401</v>
       </c>
       <c r="C290" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D290" t="s">
         <v>1834</v>
       </c>
-      <c r="D290" t="s">
+      <c r="E290" t="s">
+        <v>16</v>
+      </c>
+      <c r="F290" t="s">
         <v>1835</v>
-      </c>
-      <c r="E290" t="s">
-        <v>16</v>
-      </c>
-      <c r="F290" t="s">
-        <v>1836</v>
       </c>
       <c r="G290" t="s">
         <v>252</v>
@@ -18258,27 +18255,27 @@
         <v>854</v>
       </c>
       <c r="L290" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B291" t="s">
         <v>1401</v>
       </c>
       <c r="C291" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D291" t="s">
         <v>1839</v>
       </c>
-      <c r="D291" t="s">
+      <c r="E291" t="s">
+        <v>16</v>
+      </c>
+      <c r="F291" t="s">
         <v>1840</v>
-      </c>
-      <c r="E291" t="s">
-        <v>16</v>
-      </c>
-      <c r="F291" t="s">
-        <v>1841</v>
       </c>
       <c r="G291" t="s">
         <v>49</v>
@@ -18296,27 +18293,27 @@
         <v>809</v>
       </c>
       <c r="L291" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B292" t="s">
         <v>1401</v>
       </c>
       <c r="C292" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D292" t="s">
         <v>1844</v>
       </c>
-      <c r="D292" t="s">
+      <c r="E292" t="s">
+        <v>16</v>
+      </c>
+      <c r="F292" t="s">
         <v>1845</v>
-      </c>
-      <c r="E292" t="s">
-        <v>16</v>
-      </c>
-      <c r="F292" t="s">
-        <v>1846</v>
       </c>
       <c r="G292" t="s">
         <v>49</v>
@@ -18334,12 +18331,12 @@
         <v>809</v>
       </c>
       <c r="L292" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B293" t="s">
         <v>1401</v>
@@ -18354,10 +18351,10 @@
         <v>16</v>
       </c>
       <c r="F293" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G293" t="s">
         <v>1849</v>
-      </c>
-      <c r="G293" t="s">
-        <v>1850</v>
       </c>
       <c r="H293" t="s">
         <v>394</v>
@@ -18369,30 +18366,30 @@
         <v>21</v>
       </c>
       <c r="K293" t="s">
+        <v>1850</v>
+      </c>
+      <c r="L293" t="s">
         <v>1851</v>
-      </c>
-      <c r="L293" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B294" t="s">
         <v>1401</v>
       </c>
       <c r="C294" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D294" t="s">
         <v>1854</v>
       </c>
-      <c r="D294" t="s">
+      <c r="E294" t="s">
+        <v>16</v>
+      </c>
+      <c r="F294" t="s">
         <v>1855</v>
-      </c>
-      <c r="E294" t="s">
-        <v>16</v>
-      </c>
-      <c r="F294" t="s">
-        <v>1856</v>
       </c>
       <c r="G294" t="s">
         <v>177</v>
@@ -18410,27 +18407,27 @@
         <v>1522</v>
       </c>
       <c r="L294" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="B295" t="s">
         <v>1401</v>
       </c>
       <c r="C295" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D295" t="s">
         <v>1859</v>
       </c>
-      <c r="D295" t="s">
+      <c r="E295" t="s">
+        <v>16</v>
+      </c>
+      <c r="F295" t="s">
         <v>1860</v>
-      </c>
-      <c r="E295" t="s">
-        <v>16</v>
-      </c>
-      <c r="F295" t="s">
-        <v>1861</v>
       </c>
       <c r="G295" t="s">
         <v>1545</v>
@@ -18448,27 +18445,27 @@
         <v>1510</v>
       </c>
       <c r="L295" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B296" t="s">
         <v>1401</v>
       </c>
       <c r="C296" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D296" t="s">
         <v>1864</v>
       </c>
-      <c r="D296" t="s">
+      <c r="E296" t="s">
+        <v>16</v>
+      </c>
+      <c r="F296" t="s">
         <v>1865</v>
-      </c>
-      <c r="E296" t="s">
-        <v>16</v>
-      </c>
-      <c r="F296" t="s">
-        <v>1866</v>
       </c>
       <c r="G296" t="s">
         <v>49</v>
@@ -18483,30 +18480,30 @@
         <v>21</v>
       </c>
       <c r="K296" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="L296" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="B297" t="s">
         <v>1401</v>
       </c>
       <c r="C297" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D297" t="s">
         <v>1869</v>
       </c>
-      <c r="D297" t="s">
+      <c r="E297" t="s">
+        <v>16</v>
+      </c>
+      <c r="F297" t="s">
         <v>1870</v>
-      </c>
-      <c r="E297" t="s">
-        <v>16</v>
-      </c>
-      <c r="F297" t="s">
-        <v>1871</v>
       </c>
       <c r="G297" t="s">
         <v>177</v>
@@ -18524,18 +18521,18 @@
         <v>1522</v>
       </c>
       <c r="L297" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B298" t="s">
         <v>1401</v>
       </c>
       <c r="C298" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="D298" t="s">
         <v>1520</v>
@@ -18544,7 +18541,7 @@
         <v>16</v>
       </c>
       <c r="F298" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="G298" t="s">
         <v>738</v>
@@ -18559,30 +18556,30 @@
         <v>21</v>
       </c>
       <c r="K298" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="L298" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B299" t="s">
         <v>1401</v>
       </c>
       <c r="C299" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D299" t="s">
         <v>1878</v>
       </c>
-      <c r="D299" t="s">
+      <c r="E299" t="s">
+        <v>16</v>
+      </c>
+      <c r="F299" t="s">
         <v>1879</v>
-      </c>
-      <c r="E299" t="s">
-        <v>16</v>
-      </c>
-      <c r="F299" t="s">
-        <v>1880</v>
       </c>
       <c r="G299" t="s">
         <v>1545</v>
@@ -18600,27 +18597,27 @@
         <v>22</v>
       </c>
       <c r="L299" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B300" t="s">
         <v>1401</v>
       </c>
       <c r="C300" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D300" t="s">
         <v>1883</v>
       </c>
-      <c r="D300" t="s">
-        <v>1884</v>
-      </c>
       <c r="E300" t="s">
         <v>16</v>
       </c>
       <c r="F300" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="G300" t="s">
         <v>49</v>
@@ -18638,27 +18635,27 @@
         <v>505</v>
       </c>
       <c r="L300" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="B301" t="s">
         <v>1401</v>
       </c>
       <c r="C301" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D301" t="s">
         <v>1887</v>
       </c>
-      <c r="D301" t="s">
+      <c r="E301" t="s">
+        <v>16</v>
+      </c>
+      <c r="F301" t="s">
         <v>1888</v>
-      </c>
-      <c r="E301" t="s">
-        <v>16</v>
-      </c>
-      <c r="F301" t="s">
-        <v>1889</v>
       </c>
       <c r="G301" t="s">
         <v>738</v>
@@ -18673,33 +18670,33 @@
         <v>21</v>
       </c>
       <c r="K301" t="s">
+        <v>1889</v>
+      </c>
+      <c r="L301" t="s">
         <v>1890</v>
-      </c>
-      <c r="L301" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B302" t="s">
         <v>1892</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
         <v>1893</v>
       </c>
-      <c r="C302" t="s">
+      <c r="D302" t="s">
         <v>1894</v>
       </c>
-      <c r="D302" t="s">
+      <c r="E302" t="s">
+        <v>16</v>
+      </c>
+      <c r="F302" t="s">
         <v>1895</v>
       </c>
-      <c r="E302" t="s">
-        <v>16</v>
-      </c>
-      <c r="F302" t="s">
+      <c r="G302" t="s">
         <v>1896</v>
-      </c>
-      <c r="G302" t="s">
-        <v>1897</v>
       </c>
       <c r="H302" t="s">
         <v>253</v>
@@ -18714,30 +18711,30 @@
         <v>298</v>
       </c>
       <c r="L302" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B303" t="s">
         <v>1899</v>
       </c>
-      <c r="B303" t="s">
+      <c r="C303" t="s">
         <v>1900</v>
       </c>
-      <c r="C303" t="s">
+      <c r="D303" t="s">
         <v>1901</v>
       </c>
-      <c r="D303" t="s">
+      <c r="E303" t="s">
+        <v>16</v>
+      </c>
+      <c r="F303" t="s">
         <v>1902</v>
       </c>
-      <c r="E303" t="s">
-        <v>16</v>
-      </c>
-      <c r="F303" t="s">
+      <c r="G303" t="s">
         <v>1903</v>
-      </c>
-      <c r="G303" t="s">
-        <v>1904</v>
       </c>
       <c r="H303" t="s">
         <v>178</v>
@@ -18752,27 +18749,27 @@
         <v>137</v>
       </c>
       <c r="L303" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B304" t="s">
         <v>1906</v>
       </c>
-      <c r="B304" t="s">
+      <c r="C304" t="s">
         <v>1907</v>
       </c>
-      <c r="C304" t="s">
+      <c r="D304" t="s">
         <v>1908</v>
       </c>
-      <c r="D304" t="s">
+      <c r="E304" t="s">
+        <v>16</v>
+      </c>
+      <c r="F304" t="s">
         <v>1909</v>
-      </c>
-      <c r="E304" t="s">
-        <v>16</v>
-      </c>
-      <c r="F304" t="s">
-        <v>1910</v>
       </c>
       <c r="G304" t="s">
         <v>1357</v>
@@ -18790,27 +18787,27 @@
         <v>809</v>
       </c>
       <c r="L304" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B305" t="s">
         <v>1401</v>
       </c>
       <c r="C305" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D305" t="s">
         <v>1913</v>
       </c>
-      <c r="D305" t="s">
+      <c r="E305" t="s">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
         <v>1914</v>
-      </c>
-      <c r="E305" t="s">
-        <v>16</v>
-      </c>
-      <c r="F305" t="s">
-        <v>1915</v>
       </c>
       <c r="G305" t="s">
         <v>1357</v>
@@ -18828,27 +18825,27 @@
         <v>372</v>
       </c>
       <c r="L305" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B306" t="s">
         <v>1917</v>
       </c>
-      <c r="B306" t="s">
+      <c r="C306" t="s">
         <v>1918</v>
       </c>
-      <c r="C306" t="s">
+      <c r="D306" t="s">
         <v>1919</v>
       </c>
-      <c r="D306" t="s">
+      <c r="E306" t="s">
+        <v>16</v>
+      </c>
+      <c r="F306" t="s">
         <v>1920</v>
-      </c>
-      <c r="E306" t="s">
-        <v>16</v>
-      </c>
-      <c r="F306" t="s">
-        <v>1921</v>
       </c>
       <c r="G306" t="s">
         <v>1432</v>
@@ -18866,27 +18863,27 @@
         <v>1045</v>
       </c>
       <c r="L306" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B307" t="s">
         <v>1401</v>
       </c>
       <c r="C307" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D307" t="s">
         <v>1924</v>
       </c>
-      <c r="D307" t="s">
+      <c r="E307" t="s">
+        <v>16</v>
+      </c>
+      <c r="F307" t="s">
         <v>1925</v>
-      </c>
-      <c r="E307" t="s">
-        <v>16</v>
-      </c>
-      <c r="F307" t="s">
-        <v>1926</v>
       </c>
       <c r="G307" t="s">
         <v>177</v>
@@ -18901,30 +18898,30 @@
         <v>21</v>
       </c>
       <c r="K307" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="L307" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B308" t="s">
         <v>1401</v>
       </c>
       <c r="C308" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D308" t="s">
         <v>1929</v>
       </c>
-      <c r="D308" t="s">
+      <c r="E308" t="s">
+        <v>16</v>
+      </c>
+      <c r="F308" t="s">
         <v>1930</v>
-      </c>
-      <c r="E308" t="s">
-        <v>16</v>
-      </c>
-      <c r="F308" t="s">
-        <v>1931</v>
       </c>
       <c r="G308" t="s">
         <v>252</v>
@@ -18939,33 +18936,33 @@
         <v>21</v>
       </c>
       <c r="K308" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="L308" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B309" t="s">
         <v>1401</v>
       </c>
       <c r="C309" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D309" t="s">
         <v>1934</v>
       </c>
-      <c r="D309" t="s">
+      <c r="E309" t="s">
+        <v>16</v>
+      </c>
+      <c r="F309" t="s">
         <v>1935</v>
       </c>
-      <c r="E309" t="s">
-        <v>16</v>
-      </c>
-      <c r="F309" t="s">
-        <v>1936</v>
-      </c>
       <c r="G309" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H309" t="s">
         <v>253</v>
@@ -18977,33 +18974,33 @@
         <v>21</v>
       </c>
       <c r="K309" t="s">
+        <v>1936</v>
+      </c>
+      <c r="L309" t="s">
         <v>1937</v>
-      </c>
-      <c r="L309" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B310" t="s">
         <v>1401</v>
       </c>
       <c r="C310" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D310" t="s">
         <v>1940</v>
       </c>
-      <c r="D310" t="s">
+      <c r="E310" t="s">
+        <v>16</v>
+      </c>
+      <c r="F310" t="s">
         <v>1941</v>
       </c>
-      <c r="E310" t="s">
-        <v>16</v>
-      </c>
-      <c r="F310" t="s">
+      <c r="G310" t="s">
         <v>1942</v>
-      </c>
-      <c r="G310" t="s">
-        <v>1943</v>
       </c>
       <c r="H310" t="s">
         <v>98</v>
@@ -19015,21 +19012,21 @@
         <v>21</v>
       </c>
       <c r="K310" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="L310" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B311" t="s">
         <v>1401</v>
       </c>
       <c r="C311" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="D311" t="s">
         <v>1221</v>
@@ -19038,10 +19035,10 @@
         <v>16</v>
       </c>
       <c r="F311" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G311" t="s">
         <v>1947</v>
-      </c>
-      <c r="G311" t="s">
-        <v>1948</v>
       </c>
       <c r="H311" t="s">
         <v>841</v>
@@ -19056,27 +19053,27 @@
         <v>842</v>
       </c>
       <c r="L311" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B312" t="s">
         <v>1401</v>
       </c>
       <c r="C312" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E312" t="s">
+        <v>16</v>
+      </c>
+      <c r="F312" t="s">
         <v>1951</v>
-      </c>
-      <c r="D312" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E312" t="s">
-        <v>16</v>
-      </c>
-      <c r="F312" t="s">
-        <v>1952</v>
       </c>
       <c r="G312" t="s">
         <v>1397</v>
@@ -19091,21 +19088,21 @@
         <v>21</v>
       </c>
       <c r="K312" t="s">
+        <v>1952</v>
+      </c>
+      <c r="L312" t="s">
         <v>1953</v>
-      </c>
-      <c r="L312" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B313" t="s">
         <v>1401</v>
       </c>
       <c r="C313" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="D313" t="s">
         <v>294</v>
@@ -19129,21 +19126,21 @@
         <v>21</v>
       </c>
       <c r="K313" t="s">
+        <v>1956</v>
+      </c>
+      <c r="L313" t="s">
         <v>1957</v>
-      </c>
-      <c r="L313" t="s">
-        <v>1958</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B314" t="s">
         <v>1401</v>
       </c>
       <c r="C314" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="D314" t="s">
         <v>294</v>
@@ -19170,18 +19167,18 @@
         <v>854</v>
       </c>
       <c r="L314" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B315" t="s">
         <v>1401</v>
       </c>
       <c r="C315" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="D315" t="s">
         <v>621</v>
@@ -19190,10 +19187,10 @@
         <v>16</v>
       </c>
       <c r="F315" t="s">
+        <v>1963</v>
+      </c>
+      <c r="G315" t="s">
         <v>1964</v>
-      </c>
-      <c r="G315" t="s">
-        <v>1965</v>
       </c>
       <c r="H315" t="s">
         <v>41</v>
@@ -19208,27 +19205,27 @@
         <v>50</v>
       </c>
       <c r="L315" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B316" t="s">
         <v>1401</v>
       </c>
       <c r="C316" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E316" t="s">
+        <v>16</v>
+      </c>
+      <c r="F316" t="s">
         <v>1968</v>
-      </c>
-      <c r="D316" t="s">
-        <v>1613</v>
-      </c>
-      <c r="E316" t="s">
-        <v>16</v>
-      </c>
-      <c r="F316" t="s">
-        <v>1969</v>
       </c>
       <c r="G316" t="s">
         <v>541</v>
@@ -19246,30 +19243,30 @@
         <v>50</v>
       </c>
       <c r="L316" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B317" t="s">
         <v>1971</v>
       </c>
-      <c r="B317" t="s">
+      <c r="C317" t="s">
         <v>1972</v>
       </c>
-      <c r="C317" t="s">
+      <c r="D317" t="s">
         <v>1973</v>
       </c>
-      <c r="D317" t="s">
+      <c r="E317" t="s">
+        <v>16</v>
+      </c>
+      <c r="F317" t="s">
         <v>1974</v>
       </c>
-      <c r="E317" t="s">
-        <v>16</v>
-      </c>
-      <c r="F317" t="s">
+      <c r="G317" t="s">
         <v>1975</v>
-      </c>
-      <c r="G317" t="s">
-        <v>1976</v>
       </c>
       <c r="H317" t="s">
         <v>41</v>
@@ -19281,15 +19278,15 @@
         <v>21</v>
       </c>
       <c r="K317" t="s">
+        <v>1976</v>
+      </c>
+      <c r="L317" t="s">
         <v>1977</v>
-      </c>
-      <c r="L317" t="s">
-        <v>1978</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B318" t="s">
         <v>1401</v>
@@ -19298,13 +19295,13 @@
         <v>1343</v>
       </c>
       <c r="D318" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E318" t="s">
+        <v>16</v>
+      </c>
+      <c r="F318" t="s">
         <v>1980</v>
-      </c>
-      <c r="E318" t="s">
-        <v>16</v>
-      </c>
-      <c r="F318" t="s">
-        <v>1981</v>
       </c>
       <c r="G318" t="s">
         <v>89</v>
@@ -19322,30 +19319,30 @@
         <v>107</v>
       </c>
       <c r="L318" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B319" t="s">
         <v>1983</v>
       </c>
-      <c r="B319" t="s">
+      <c r="C319" t="s">
         <v>1984</v>
       </c>
-      <c r="C319" t="s">
+      <c r="D319" t="s">
         <v>1985</v>
       </c>
-      <c r="D319" t="s">
+      <c r="E319" t="s">
+        <v>16</v>
+      </c>
+      <c r="F319" t="s">
         <v>1986</v>
       </c>
-      <c r="E319" t="s">
-        <v>16</v>
-      </c>
-      <c r="F319" t="s">
+      <c r="G319" t="s">
         <v>1987</v>
-      </c>
-      <c r="G319" t="s">
-        <v>1988</v>
       </c>
       <c r="H319" t="s">
         <v>253</v>
@@ -19357,33 +19354,33 @@
         <v>21</v>
       </c>
       <c r="K319" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="L319" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B320" t="s">
         <v>1401</v>
       </c>
       <c r="C320" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D320" t="s">
         <v>1991</v>
       </c>
-      <c r="D320" t="s">
+      <c r="E320" t="s">
+        <v>16</v>
+      </c>
+      <c r="F320" t="s">
         <v>1992</v>
       </c>
-      <c r="E320" t="s">
-        <v>16</v>
-      </c>
-      <c r="F320" t="s">
+      <c r="G320" t="s">
         <v>1993</v>
-      </c>
-      <c r="G320" t="s">
-        <v>1994</v>
       </c>
       <c r="H320" t="s">
         <v>253</v>
@@ -19395,30 +19392,30 @@
         <v>21</v>
       </c>
       <c r="K320" t="s">
+        <v>1994</v>
+      </c>
+      <c r="L320" t="s">
         <v>1995</v>
-      </c>
-      <c r="L320" t="s">
-        <v>1996</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B321" t="s">
         <v>1401</v>
       </c>
       <c r="C321" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D321" t="s">
         <v>1998</v>
       </c>
-      <c r="D321" t="s">
+      <c r="E321" t="s">
+        <v>16</v>
+      </c>
+      <c r="F321" t="s">
         <v>1999</v>
-      </c>
-      <c r="E321" t="s">
-        <v>16</v>
-      </c>
-      <c r="F321" t="s">
-        <v>2000</v>
       </c>
       <c r="G321" t="s">
         <v>252</v>
@@ -19436,30 +19433,30 @@
         <v>1411</v>
       </c>
       <c r="L321" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B322" t="s">
         <v>2002</v>
       </c>
-      <c r="B322" t="s">
+      <c r="C322" t="s">
         <v>2003</v>
       </c>
-      <c r="C322" t="s">
+      <c r="D322" t="s">
         <v>2004</v>
       </c>
-      <c r="D322" t="s">
+      <c r="E322" t="s">
+        <v>16</v>
+      </c>
+      <c r="F322" t="s">
         <v>2005</v>
       </c>
-      <c r="E322" t="s">
-        <v>16</v>
-      </c>
-      <c r="F322" t="s">
+      <c r="G322" t="s">
         <v>2006</v>
-      </c>
-      <c r="G322" t="s">
-        <v>2007</v>
       </c>
       <c r="H322" t="s">
         <v>160</v>
@@ -19474,27 +19471,27 @@
         <v>1444</v>
       </c>
       <c r="L322" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B323" t="s">
         <v>1401</v>
       </c>
       <c r="C323" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D323" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E323" t="s">
+        <v>16</v>
+      </c>
+      <c r="F323" t="s">
         <v>2010</v>
-      </c>
-      <c r="D323" t="s">
-        <v>1717</v>
-      </c>
-      <c r="E323" t="s">
-        <v>16</v>
-      </c>
-      <c r="F323" t="s">
-        <v>2011</v>
       </c>
       <c r="G323" t="s">
         <v>252</v>
@@ -19509,30 +19506,30 @@
         <v>21</v>
       </c>
       <c r="K323" t="s">
+        <v>2011</v>
+      </c>
+      <c r="L323" t="s">
         <v>2012</v>
-      </c>
-      <c r="L323" t="s">
-        <v>2013</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B324" t="s">
         <v>1401</v>
       </c>
       <c r="C324" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D324" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E324" t="s">
+        <v>16</v>
+      </c>
+      <c r="F324" t="s">
         <v>2015</v>
-      </c>
-      <c r="D324" t="s">
-        <v>1787</v>
-      </c>
-      <c r="E324" t="s">
-        <v>16</v>
-      </c>
-      <c r="F324" t="s">
-        <v>2016</v>
       </c>
       <c r="G324" t="s">
         <v>1397</v>
@@ -19550,30 +19547,30 @@
         <v>298</v>
       </c>
       <c r="L324" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B325" t="s">
         <v>2018</v>
       </c>
-      <c r="B325" t="s">
+      <c r="C325" t="s">
         <v>2019</v>
       </c>
-      <c r="C325" t="s">
+      <c r="D325" t="s">
         <v>2020</v>
       </c>
-      <c r="D325" t="s">
+      <c r="E325" t="s">
+        <v>16</v>
+      </c>
+      <c r="F325" t="s">
         <v>2021</v>
       </c>
-      <c r="E325" t="s">
-        <v>16</v>
-      </c>
-      <c r="F325" t="s">
+      <c r="G325" t="s">
         <v>2022</v>
-      </c>
-      <c r="G325" t="s">
-        <v>2023</v>
       </c>
       <c r="H325" t="s">
         <v>253</v>
@@ -19585,30 +19582,30 @@
         <v>21</v>
       </c>
       <c r="K325" t="s">
+        <v>2023</v>
+      </c>
+      <c r="L325" t="s">
         <v>2024</v>
-      </c>
-      <c r="L325" t="s">
-        <v>2025</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B326" t="s">
         <v>1401</v>
       </c>
       <c r="C326" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D326" t="s">
         <v>2027</v>
       </c>
-      <c r="D326" t="s">
+      <c r="E326" t="s">
+        <v>16</v>
+      </c>
+      <c r="F326" t="s">
         <v>2028</v>
-      </c>
-      <c r="E326" t="s">
-        <v>16</v>
-      </c>
-      <c r="F326" t="s">
-        <v>2029</v>
       </c>
       <c r="G326" t="s">
         <v>1357</v>
@@ -19626,30 +19623,30 @@
         <v>254</v>
       </c>
       <c r="L326" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B327" t="s">
         <v>1401</v>
       </c>
       <c r="C327" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D327" t="s">
         <v>2032</v>
       </c>
-      <c r="D327" t="s">
+      <c r="E327" t="s">
+        <v>16</v>
+      </c>
+      <c r="F327" t="s">
         <v>2033</v>
       </c>
-      <c r="E327" t="s">
-        <v>16</v>
-      </c>
-      <c r="F327" t="s">
+      <c r="G327" t="s">
         <v>2034</v>
-      </c>
-      <c r="G327" t="s">
-        <v>2035</v>
       </c>
       <c r="H327" t="s">
         <v>253</v>
@@ -19661,30 +19658,30 @@
         <v>21</v>
       </c>
       <c r="K327" t="s">
+        <v>2035</v>
+      </c>
+      <c r="L327" t="s">
         <v>2036</v>
-      </c>
-      <c r="L327" t="s">
-        <v>2037</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B328" t="s">
         <v>2038</v>
       </c>
-      <c r="B328" t="s">
+      <c r="C328" t="s">
         <v>2039</v>
       </c>
-      <c r="C328" t="s">
+      <c r="D328" t="s">
         <v>2040</v>
       </c>
-      <c r="D328" t="s">
+      <c r="E328" t="s">
+        <v>16</v>
+      </c>
+      <c r="F328" t="s">
         <v>2041</v>
-      </c>
-      <c r="E328" t="s">
-        <v>16</v>
-      </c>
-      <c r="F328" t="s">
-        <v>2042</v>
       </c>
       <c r="G328" t="s">
         <v>1357</v>
@@ -19702,27 +19699,27 @@
         <v>518</v>
       </c>
       <c r="L328" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B329" t="s">
         <v>2044</v>
       </c>
-      <c r="B329" t="s">
+      <c r="C329" t="s">
         <v>2045</v>
       </c>
-      <c r="C329" t="s">
+      <c r="D329" t="s">
         <v>2046</v>
       </c>
-      <c r="D329" t="s">
+      <c r="E329" t="s">
+        <v>16</v>
+      </c>
+      <c r="F329" t="s">
         <v>2047</v>
-      </c>
-      <c r="E329" t="s">
-        <v>16</v>
-      </c>
-      <c r="F329" t="s">
-        <v>2048</v>
       </c>
       <c r="G329" t="s">
         <v>1376</v>
@@ -19740,27 +19737,27 @@
         <v>298</v>
       </c>
       <c r="L329" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B330" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C330" t="s">
         <v>2050</v>
       </c>
-      <c r="B330" t="s">
-        <v>2045</v>
-      </c>
-      <c r="C330" t="s">
-        <v>2051</v>
-      </c>
       <c r="D330" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E330" t="s">
+        <v>16</v>
+      </c>
+      <c r="F330" t="s">
         <v>2047</v>
-      </c>
-      <c r="E330" t="s">
-        <v>16</v>
-      </c>
-      <c r="F330" t="s">
-        <v>2048</v>
       </c>
       <c r="G330" t="s">
         <v>1376</v>
@@ -19778,15 +19775,15 @@
         <v>298</v>
       </c>
       <c r="L330" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B331" t="s">
         <v>2053</v>
-      </c>
-      <c r="B331" t="s">
-        <v>2054</v>
       </c>
       <c r="C331" t="s">
         <v>1499</v>
@@ -19821,25 +19818,25 @@
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B332" t="s">
         <v>1401</v>
       </c>
       <c r="C332" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D332" t="s">
         <v>2056</v>
       </c>
-      <c r="D332" t="s">
+      <c r="E332" t="s">
+        <v>16</v>
+      </c>
+      <c r="F332" t="s">
         <v>2057</v>
       </c>
-      <c r="E332" t="s">
-        <v>16</v>
-      </c>
-      <c r="F332" t="s">
+      <c r="G332" t="s">
         <v>2058</v>
-      </c>
-      <c r="G332" t="s">
-        <v>2059</v>
       </c>
       <c r="H332" t="s">
         <v>160</v>
@@ -19851,30 +19848,30 @@
         <v>21</v>
       </c>
       <c r="K332" t="s">
+        <v>2059</v>
+      </c>
+      <c r="L332" t="s">
         <v>2060</v>
-      </c>
-      <c r="L332" t="s">
-        <v>2061</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B333" t="s">
         <v>2062</v>
       </c>
-      <c r="B333" t="s">
+      <c r="C333" t="s">
         <v>2063</v>
       </c>
-      <c r="C333" t="s">
+      <c r="D333" t="s">
         <v>2064</v>
       </c>
-      <c r="D333" t="s">
+      <c r="E333" t="s">
+        <v>16</v>
+      </c>
+      <c r="F333" t="s">
         <v>2065</v>
-      </c>
-      <c r="E333" t="s">
-        <v>16</v>
-      </c>
-      <c r="F333" t="s">
-        <v>2066</v>
       </c>
       <c r="G333" t="s">
         <v>1357</v>
@@ -19892,18 +19889,18 @@
         <v>1390</v>
       </c>
       <c r="L333" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="B334" t="s">
         <v>1401</v>
       </c>
       <c r="C334" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="D334" t="s">
         <v>294</v>
@@ -19912,7 +19909,7 @@
         <v>16</v>
       </c>
       <c r="F334" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="G334" t="s">
         <v>252</v>
@@ -19927,30 +19924,30 @@
         <v>21</v>
       </c>
       <c r="K334" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="L334" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="B335" t="s">
         <v>1401</v>
       </c>
       <c r="C335" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E335" t="s">
+        <v>16</v>
+      </c>
+      <c r="F335" t="s">
         <v>2073</v>
-      </c>
-      <c r="D335" t="s">
-        <v>1717</v>
-      </c>
-      <c r="E335" t="s">
-        <v>16</v>
-      </c>
-      <c r="F335" t="s">
-        <v>2074</v>
       </c>
       <c r="G335" t="s">
         <v>429</v>
@@ -19968,27 +19965,27 @@
         <v>1411</v>
       </c>
       <c r="L335" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B336" t="s">
         <v>2076</v>
       </c>
-      <c r="B336" t="s">
+      <c r="C336" t="s">
         <v>2077</v>
       </c>
-      <c r="C336" t="s">
+      <c r="D336" t="s">
         <v>2078</v>
       </c>
-      <c r="D336" t="s">
+      <c r="E336" t="s">
+        <v>16</v>
+      </c>
+      <c r="F336" t="s">
         <v>2079</v>
-      </c>
-      <c r="E336" t="s">
-        <v>16</v>
-      </c>
-      <c r="F336" t="s">
-        <v>2080</v>
       </c>
       <c r="G336" t="s">
         <v>252</v>
@@ -20006,30 +20003,30 @@
         <v>1411</v>
       </c>
       <c r="L336" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B337" t="s">
         <v>2082</v>
       </c>
-      <c r="B337" t="s">
+      <c r="C337" t="s">
         <v>2083</v>
       </c>
-      <c r="C337" t="s">
+      <c r="D337" t="s">
         <v>2084</v>
       </c>
-      <c r="D337" t="s">
+      <c r="E337" t="s">
+        <v>16</v>
+      </c>
+      <c r="F337" t="s">
         <v>2085</v>
       </c>
-      <c r="E337" t="s">
-        <v>16</v>
-      </c>
-      <c r="F337" t="s">
+      <c r="G337" t="s">
         <v>2086</v>
-      </c>
-      <c r="G337" t="s">
-        <v>2087</v>
       </c>
       <c r="H337" t="s">
         <v>588</v>
@@ -20041,15 +20038,15 @@
         <v>21</v>
       </c>
       <c r="K337" t="s">
+        <v>2087</v>
+      </c>
+      <c r="L337" t="s">
         <v>2088</v>
-      </c>
-      <c r="L337" t="s">
-        <v>2089</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="B338" t="s">
         <v>1401</v>
@@ -20064,10 +20061,10 @@
         <v>16</v>
       </c>
       <c r="F338" t="s">
+        <v>2090</v>
+      </c>
+      <c r="G338" t="s">
         <v>2091</v>
-      </c>
-      <c r="G338" t="s">
-        <v>2092</v>
       </c>
       <c r="H338" t="s">
         <v>41</v>
@@ -20087,7 +20084,7 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="B339" t="s">
         <v>1401</v>
@@ -20102,10 +20099,10 @@
         <v>16</v>
       </c>
       <c r="F339" t="s">
+        <v>2090</v>
+      </c>
+      <c r="G339" t="s">
         <v>2091</v>
-      </c>
-      <c r="G339" t="s">
-        <v>2092</v>
       </c>
       <c r="H339" t="s">
         <v>41</v>
@@ -20125,7 +20122,7 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="B340" t="s">
         <v>1401</v>
@@ -20140,10 +20137,10 @@
         <v>16</v>
       </c>
       <c r="F340" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="G340" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="H340" t="s">
         <v>41</v>
@@ -20163,22 +20160,22 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B341" t="s">
         <v>1401</v>
       </c>
       <c r="C341" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D341" t="s">
+        <v>1894</v>
+      </c>
+      <c r="E341" t="s">
+        <v>16</v>
+      </c>
+      <c r="F341" t="s">
         <v>2097</v>
-      </c>
-      <c r="D341" t="s">
-        <v>1895</v>
-      </c>
-      <c r="E341" t="s">
-        <v>16</v>
-      </c>
-      <c r="F341" t="s">
-        <v>2098</v>
       </c>
       <c r="G341" t="s">
         <v>1357</v>
@@ -20196,27 +20193,27 @@
         <v>298</v>
       </c>
       <c r="L341" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B342" t="s">
         <v>2100</v>
       </c>
-      <c r="B342" t="s">
+      <c r="C342" t="s">
         <v>2101</v>
       </c>
-      <c r="C342" t="s">
+      <c r="D342" t="s">
+        <v>16</v>
+      </c>
+      <c r="E342" t="s">
+        <v>16</v>
+      </c>
+      <c r="F342" t="s">
         <v>2102</v>
-      </c>
-      <c r="D342" t="s">
-        <v>16</v>
-      </c>
-      <c r="E342" t="s">
-        <v>16</v>
-      </c>
-      <c r="F342" t="s">
-        <v>2103</v>
       </c>
       <c r="G342" t="s">
         <v>317</v>
@@ -20231,30 +20228,30 @@
         <v>21</v>
       </c>
       <c r="K342" t="s">
+        <v>2103</v>
+      </c>
+      <c r="L342" t="s">
         <v>2104</v>
-      </c>
-      <c r="L342" t="s">
-        <v>2105</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B343" t="s">
         <v>2106</v>
       </c>
-      <c r="B343" t="s">
+      <c r="C343" t="s">
         <v>2107</v>
       </c>
-      <c r="C343" t="s">
+      <c r="D343" t="s">
         <v>2108</v>
       </c>
-      <c r="D343" t="s">
+      <c r="E343" t="s">
+        <v>16</v>
+      </c>
+      <c r="F343" t="s">
         <v>2109</v>
-      </c>
-      <c r="E343" t="s">
-        <v>16</v>
-      </c>
-      <c r="F343" t="s">
-        <v>2110</v>
       </c>
       <c r="G343" t="s">
         <v>1357</v>
@@ -20272,33 +20269,33 @@
         <v>809</v>
       </c>
       <c r="L343" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="B344" t="s">
         <v>1401</v>
       </c>
       <c r="C344" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D344" t="s">
         <v>2113</v>
       </c>
-      <c r="D344" t="s">
+      <c r="E344" t="s">
+        <v>16</v>
+      </c>
+      <c r="F344" t="s">
         <v>2114</v>
       </c>
-      <c r="E344" t="s">
-        <v>16</v>
-      </c>
-      <c r="F344" t="s">
+      <c r="G344" t="s">
         <v>2115</v>
       </c>
-      <c r="G344" t="s">
+      <c r="H344" t="s">
         <v>2116</v>
-      </c>
-      <c r="H344" t="s">
-        <v>2117</v>
       </c>
       <c r="I344" t="s">
         <v>20</v>
@@ -20310,33 +20307,33 @@
         <v>283</v>
       </c>
       <c r="L344" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B345" t="s">
         <v>1401</v>
       </c>
       <c r="C345" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D345" t="s">
         <v>2120</v>
       </c>
-      <c r="D345" t="s">
-        <v>2121</v>
-      </c>
       <c r="E345" t="s">
         <v>16</v>
       </c>
       <c r="F345" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G345" t="s">
         <v>2115</v>
       </c>
-      <c r="G345" t="s">
+      <c r="H345" t="s">
         <v>2116</v>
-      </c>
-      <c r="H345" t="s">
-        <v>2117</v>
       </c>
       <c r="I345" t="s">
         <v>20</v>
@@ -20348,27 +20345,27 @@
         <v>395</v>
       </c>
       <c r="L345" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B346" t="s">
         <v>2123</v>
       </c>
-      <c r="B346" t="s">
+      <c r="C346" t="s">
         <v>2124</v>
       </c>
-      <c r="C346" t="s">
+      <c r="D346" t="s">
         <v>2125</v>
       </c>
-      <c r="D346" t="s">
+      <c r="E346" t="s">
+        <v>16</v>
+      </c>
+      <c r="F346" t="s">
         <v>2126</v>
-      </c>
-      <c r="E346" t="s">
-        <v>16</v>
-      </c>
-      <c r="F346" t="s">
-        <v>2127</v>
       </c>
       <c r="G346" t="s">
         <v>49</v>
@@ -20383,33 +20380,33 @@
         <v>21</v>
       </c>
       <c r="K346" t="s">
+        <v>2127</v>
+      </c>
+      <c r="L346" t="s">
         <v>2128</v>
-      </c>
-      <c r="L346" t="s">
-        <v>2129</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="B347" t="s">
         <v>1393</v>
       </c>
       <c r="C347" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="D347" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E347" t="s">
+        <v>16</v>
+      </c>
+      <c r="F347" t="s">
         <v>1787</v>
       </c>
-      <c r="E347" t="s">
-        <v>16</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1788</v>
-      </c>
       <c r="G347" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H347" t="s">
         <v>253</v>
@@ -20424,30 +20421,30 @@
         <v>298</v>
       </c>
       <c r="L347" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B348" t="s">
         <v>1401</v>
       </c>
       <c r="C348" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D348" t="s">
         <v>2134</v>
       </c>
-      <c r="D348" t="s">
+      <c r="E348" t="s">
+        <v>16</v>
+      </c>
+      <c r="F348" t="s">
         <v>2135</v>
       </c>
-      <c r="E348" t="s">
-        <v>16</v>
-      </c>
-      <c r="F348" t="s">
+      <c r="G348" t="s">
         <v>2136</v>
-      </c>
-      <c r="G348" t="s">
-        <v>2137</v>
       </c>
       <c r="H348" t="s">
         <v>253</v>
@@ -20459,30 +20456,30 @@
         <v>21</v>
       </c>
       <c r="K348" t="s">
+        <v>2137</v>
+      </c>
+      <c r="L348" t="s">
         <v>2138</v>
-      </c>
-      <c r="L348" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="B349" t="s">
         <v>1401</v>
       </c>
       <c r="C349" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D349" t="s">
         <v>2141</v>
       </c>
-      <c r="D349" t="s">
+      <c r="E349" t="s">
+        <v>16</v>
+      </c>
+      <c r="F349" t="s">
         <v>2142</v>
-      </c>
-      <c r="E349" t="s">
-        <v>16</v>
-      </c>
-      <c r="F349" t="s">
-        <v>2143</v>
       </c>
       <c r="G349" t="s">
         <v>177</v>
@@ -20500,27 +20497,27 @@
         <v>1522</v>
       </c>
       <c r="L349" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B350" t="s">
         <v>1401</v>
       </c>
       <c r="C350" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D350" t="s">
         <v>2146</v>
       </c>
-      <c r="D350" t="s">
+      <c r="E350" t="s">
+        <v>16</v>
+      </c>
+      <c r="F350" t="s">
         <v>2147</v>
-      </c>
-      <c r="E350" t="s">
-        <v>16</v>
-      </c>
-      <c r="F350" t="s">
-        <v>2148</v>
       </c>
       <c r="G350" t="s">
         <v>177</v>
@@ -20535,30 +20532,30 @@
         <v>21</v>
       </c>
       <c r="K350" t="s">
+        <v>2148</v>
+      </c>
+      <c r="L350" t="s">
         <v>2149</v>
-      </c>
-      <c r="L350" t="s">
-        <v>2150</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B351" t="s">
         <v>1401</v>
       </c>
       <c r="C351" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D351" t="s">
         <v>2152</v>
       </c>
-      <c r="D351" t="s">
+      <c r="E351" t="s">
+        <v>16</v>
+      </c>
+      <c r="F351" t="s">
         <v>2153</v>
-      </c>
-      <c r="E351" t="s">
-        <v>16</v>
-      </c>
-      <c r="F351" t="s">
-        <v>2154</v>
       </c>
       <c r="G351" t="s">
         <v>49</v>
@@ -20573,30 +20570,30 @@
         <v>21</v>
       </c>
       <c r="K351" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="L351" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="B352" t="s">
         <v>1401</v>
       </c>
       <c r="C352" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D352" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E352" t="s">
+        <v>16</v>
+      </c>
+      <c r="F352" t="s">
         <v>2157</v>
-      </c>
-      <c r="D352" t="s">
-        <v>2041</v>
-      </c>
-      <c r="E352" t="s">
-        <v>16</v>
-      </c>
-      <c r="F352" t="s">
-        <v>2158</v>
       </c>
       <c r="G352" t="s">
         <v>1357</v>
@@ -20614,30 +20611,30 @@
         <v>518</v>
       </c>
       <c r="L352" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B353" t="s">
         <v>2160</v>
       </c>
-      <c r="B353" t="s">
+      <c r="C353" t="s">
         <v>2161</v>
       </c>
-      <c r="C353" t="s">
+      <c r="D353" t="s">
+        <v>1985</v>
+      </c>
+      <c r="E353" t="s">
+        <v>16</v>
+      </c>
+      <c r="F353" t="s">
         <v>2162</v>
       </c>
-      <c r="D353" t="s">
-        <v>1986</v>
-      </c>
-      <c r="E353" t="s">
-        <v>16</v>
-      </c>
-      <c r="F353" t="s">
+      <c r="G353" t="s">
         <v>2163</v>
-      </c>
-      <c r="G353" t="s">
-        <v>2164</v>
       </c>
       <c r="H353" t="s">
         <v>394</v>
@@ -20652,30 +20649,30 @@
         <v>33</v>
       </c>
       <c r="L353" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B354" t="s">
         <v>2166</v>
       </c>
-      <c r="B354" t="s">
+      <c r="C354" t="s">
         <v>2167</v>
       </c>
-      <c r="C354" t="s">
+      <c r="D354" t="s">
         <v>2168</v>
       </c>
-      <c r="D354" t="s">
+      <c r="E354" t="s">
+        <v>16</v>
+      </c>
+      <c r="F354" t="s">
         <v>2169</v>
       </c>
-      <c r="E354" t="s">
-        <v>16</v>
-      </c>
-      <c r="F354" t="s">
+      <c r="G354" t="s">
         <v>2170</v>
-      </c>
-      <c r="G354" t="s">
-        <v>2171</v>
       </c>
       <c r="H354" t="s">
         <v>253</v>
@@ -20690,18 +20687,18 @@
         <v>1358</v>
       </c>
       <c r="L354" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B355" t="s">
         <v>1447</v>
       </c>
       <c r="C355" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="D355" t="s">
         <v>1449</v>
@@ -20710,45 +20707,45 @@
         <v>16</v>
       </c>
       <c r="F355" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="G355" t="s">
         <v>1432</v>
       </c>
       <c r="H355" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I355" t="s">
+        <v>20</v>
+      </c>
+      <c r="J355" t="s">
+        <v>21</v>
+      </c>
+      <c r="K355" t="s">
         <v>2176</v>
       </c>
-      <c r="I355" t="s">
-        <v>20</v>
-      </c>
-      <c r="J355" t="s">
-        <v>21</v>
-      </c>
-      <c r="K355" t="s">
+      <c r="L355" t="s">
         <v>2177</v>
-      </c>
-      <c r="L355" t="s">
-        <v>2178</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B356" t="s">
         <v>2179</v>
       </c>
-      <c r="B356" t="s">
+      <c r="C356" t="s">
         <v>2180</v>
       </c>
-      <c r="C356" t="s">
+      <c r="D356" t="s">
         <v>2181</v>
       </c>
-      <c r="D356" t="s">
+      <c r="E356" t="s">
+        <v>16</v>
+      </c>
+      <c r="F356" t="s">
         <v>2182</v>
-      </c>
-      <c r="E356" t="s">
-        <v>16</v>
-      </c>
-      <c r="F356" t="s">
-        <v>2183</v>
       </c>
       <c r="G356" t="s">
         <v>252</v>
@@ -20763,33 +20760,33 @@
         <v>21</v>
       </c>
       <c r="K356" t="s">
+        <v>2183</v>
+      </c>
+      <c r="L356" t="s">
         <v>2184</v>
-      </c>
-      <c r="L356" t="s">
-        <v>2185</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B357" t="s">
         <v>2186</v>
       </c>
-      <c r="B357" t="s">
+      <c r="C357" t="s">
         <v>2187</v>
       </c>
-      <c r="C357" t="s">
+      <c r="D357" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E357" t="s">
+        <v>16</v>
+      </c>
+      <c r="F357" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G357" t="s">
         <v>2188</v>
-      </c>
-      <c r="D357" t="s">
-        <v>1769</v>
-      </c>
-      <c r="E357" t="s">
-        <v>16</v>
-      </c>
-      <c r="F357" t="s">
-        <v>1770</v>
-      </c>
-      <c r="G357" t="s">
-        <v>2189</v>
       </c>
       <c r="H357" t="s">
         <v>253</v>
@@ -20804,27 +20801,27 @@
         <v>1358</v>
       </c>
       <c r="L357" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="B358" t="s">
         <v>1401</v>
       </c>
       <c r="C358" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D358" t="s">
         <v>2192</v>
       </c>
-      <c r="D358" t="s">
+      <c r="E358" t="s">
+        <v>16</v>
+      </c>
+      <c r="F358" t="s">
         <v>2193</v>
-      </c>
-      <c r="E358" t="s">
-        <v>16</v>
-      </c>
-      <c r="F358" t="s">
-        <v>2194</v>
       </c>
       <c r="G358" t="s">
         <v>252</v>
@@ -20842,27 +20839,27 @@
         <v>1411</v>
       </c>
       <c r="L358" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="B359" t="s">
         <v>1401</v>
       </c>
       <c r="C359" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D359" t="s">
         <v>2197</v>
       </c>
-      <c r="D359" t="s">
+      <c r="E359" t="s">
+        <v>16</v>
+      </c>
+      <c r="F359" t="s">
         <v>2198</v>
-      </c>
-      <c r="E359" t="s">
-        <v>16</v>
-      </c>
-      <c r="F359" t="s">
-        <v>2199</v>
       </c>
       <c r="G359" t="s">
         <v>1357</v>
@@ -20880,27 +20877,27 @@
         <v>809</v>
       </c>
       <c r="L359" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B360" t="s">
         <v>1401</v>
       </c>
       <c r="C360" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="D360" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E360" t="s">
         <v>16</v>
       </c>
       <c r="F360" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="G360" t="s">
         <v>252</v>
@@ -20918,27 +20915,27 @@
         <v>170</v>
       </c>
       <c r="L360" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B361" t="s">
         <v>2204</v>
       </c>
-      <c r="B361" t="s">
+      <c r="C361" t="s">
         <v>2205</v>
       </c>
-      <c r="C361" t="s">
+      <c r="D361" t="s">
         <v>2206</v>
       </c>
-      <c r="D361" t="s">
+      <c r="E361" t="s">
+        <v>16</v>
+      </c>
+      <c r="F361" t="s">
         <v>2207</v>
-      </c>
-      <c r="E361" t="s">
-        <v>16</v>
-      </c>
-      <c r="F361" t="s">
-        <v>2208</v>
       </c>
       <c r="G361" t="s">
         <v>114</v>
@@ -20953,24 +20950,24 @@
         <v>21</v>
       </c>
       <c r="K361" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="L361" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B362" t="s">
         <v>1401</v>
       </c>
       <c r="C362" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D362" t="s">
         <v>2211</v>
-      </c>
-      <c r="D362" t="s">
-        <v>2212</v>
       </c>
       <c r="E362" t="s">
         <v>16</v>
@@ -20982,7 +20979,7 @@
         <v>1457</v>
       </c>
       <c r="H362" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="I362" t="s">
         <v>20</v>
@@ -20994,33 +20991,33 @@
         <v>1390</v>
       </c>
       <c r="L362" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="B363" t="s">
         <v>1401</v>
       </c>
       <c r="C363" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D363" t="s">
         <v>2216</v>
       </c>
-      <c r="D363" t="s">
+      <c r="E363" t="s">
+        <v>16</v>
+      </c>
+      <c r="F363" t="s">
         <v>2217</v>
-      </c>
-      <c r="E363" t="s">
-        <v>16</v>
-      </c>
-      <c r="F363" t="s">
-        <v>2218</v>
       </c>
       <c r="G363" t="s">
         <v>492</v>
       </c>
       <c r="H363" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="I363" t="s">
         <v>20</v>
@@ -21032,30 +21029,30 @@
         <v>208</v>
       </c>
       <c r="L363" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B364" t="s">
         <v>1401</v>
       </c>
       <c r="C364" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D364" t="s">
         <v>2222</v>
       </c>
-      <c r="D364" t="s">
+      <c r="E364" t="s">
+        <v>16</v>
+      </c>
+      <c r="F364" t="s">
         <v>2223</v>
       </c>
-      <c r="E364" t="s">
-        <v>16</v>
-      </c>
-      <c r="F364" t="s">
+      <c r="G364" t="s">
         <v>2224</v>
-      </c>
-      <c r="G364" t="s">
-        <v>2225</v>
       </c>
       <c r="H364" t="s">
         <v>236</v>
@@ -21070,30 +21067,30 @@
         <v>208</v>
       </c>
       <c r="L364" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B365" t="s">
         <v>1401</v>
       </c>
       <c r="C365" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D365" t="s">
         <v>2228</v>
       </c>
-      <c r="D365" t="s">
+      <c r="E365" t="s">
+        <v>16</v>
+      </c>
+      <c r="F365" t="s">
         <v>2229</v>
       </c>
-      <c r="E365" t="s">
-        <v>16</v>
-      </c>
-      <c r="F365" t="s">
+      <c r="G365" t="s">
         <v>2230</v>
-      </c>
-      <c r="G365" t="s">
-        <v>2231</v>
       </c>
       <c r="H365" t="s">
         <v>41</v>
@@ -21108,30 +21105,30 @@
         <v>50</v>
       </c>
       <c r="L365" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B366" t="s">
         <v>1401</v>
       </c>
       <c r="C366" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D366" t="s">
         <v>2234</v>
       </c>
-      <c r="D366" t="s">
+      <c r="E366" t="s">
+        <v>16</v>
+      </c>
+      <c r="F366" t="s">
         <v>2235</v>
       </c>
-      <c r="E366" t="s">
-        <v>16</v>
-      </c>
-      <c r="F366" t="s">
+      <c r="G366" t="s">
         <v>2236</v>
-      </c>
-      <c r="G366" t="s">
-        <v>2237</v>
       </c>
       <c r="H366" t="s">
         <v>41</v>
@@ -21146,12 +21143,12 @@
         <v>809</v>
       </c>
       <c r="L366" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B367" t="s">
         <v>1401</v>
@@ -21160,13 +21157,13 @@
         <v>212</v>
       </c>
       <c r="D367" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E367" t="s">
+        <v>16</v>
+      </c>
+      <c r="F367" t="s">
         <v>2240</v>
-      </c>
-      <c r="E367" t="s">
-        <v>16</v>
-      </c>
-      <c r="F367" t="s">
-        <v>2241</v>
       </c>
       <c r="G367" t="s">
         <v>215</v>
@@ -21184,33 +21181,33 @@
         <v>170</v>
       </c>
       <c r="L367" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B368" t="s">
         <v>2243</v>
       </c>
-      <c r="B368" t="s">
+      <c r="C368" t="s">
         <v>2244</v>
       </c>
-      <c r="C368" t="s">
+      <c r="D368" t="s">
         <v>2245</v>
       </c>
-      <c r="D368" t="s">
+      <c r="E368" t="s">
+        <v>16</v>
+      </c>
+      <c r="F368" t="s">
         <v>2246</v>
       </c>
-      <c r="E368" t="s">
-        <v>16</v>
-      </c>
-      <c r="F368" t="s">
+      <c r="G368" t="s">
+        <v>2246</v>
+      </c>
+      <c r="H368" t="s">
         <v>2247</v>
-      </c>
-      <c r="G368" t="s">
-        <v>2247</v>
-      </c>
-      <c r="H368" t="s">
-        <v>2248</v>
       </c>
       <c r="I368" t="s">
         <v>1074</v>
@@ -21227,7 +21224,7 @@
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="B369" t="s">
         <v>1401</v>
@@ -21265,28 +21262,28 @@
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B370" t="s">
         <v>2250</v>
       </c>
-      <c r="B370" t="s">
+      <c r="C370" t="s">
+        <v>16</v>
+      </c>
+      <c r="D370" t="s">
         <v>2251</v>
       </c>
-      <c r="C370" t="s">
-        <v>16</v>
-      </c>
-      <c r="D370" t="s">
+      <c r="E370" t="s">
+        <v>16</v>
+      </c>
+      <c r="F370" t="s">
+        <v>16</v>
+      </c>
+      <c r="G370" t="s">
+        <v>16</v>
+      </c>
+      <c r="H370" t="s">
         <v>2252</v>
-      </c>
-      <c r="E370" t="s">
-        <v>16</v>
-      </c>
-      <c r="F370" t="s">
-        <v>16</v>
-      </c>
-      <c r="G370" t="s">
-        <v>16</v>
-      </c>
-      <c r="H370" t="s">
-        <v>2253</v>
       </c>
       <c r="I370" t="s">
         <v>1074</v>
@@ -21303,7 +21300,7 @@
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="B371" t="s">
         <v>1401</v>
@@ -21312,13 +21309,13 @@
         <v>16</v>
       </c>
       <c r="D371" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="E371" t="s">
         <v>16</v>
       </c>
       <c r="F371" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="G371" t="s">
         <v>89</v>
@@ -21341,7 +21338,7 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="B372" t="s">
         <v>1401</v>
@@ -21350,16 +21347,16 @@
         <v>16</v>
       </c>
       <c r="D372" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E372" t="s">
+        <v>16</v>
+      </c>
+      <c r="F372" t="s">
         <v>2257</v>
       </c>
-      <c r="E372" t="s">
-        <v>16</v>
-      </c>
-      <c r="F372" t="s">
+      <c r="G372" t="s">
         <v>2258</v>
-      </c>
-      <c r="G372" t="s">
-        <v>2259</v>
       </c>
       <c r="H372" t="s">
         <v>115</v>
@@ -21371,15 +21368,15 @@
         <v>32</v>
       </c>
       <c r="K372" t="s">
+        <v>2259</v>
+      </c>
+      <c r="L372" t="s">
         <v>2260</v>
-      </c>
-      <c r="L372" t="s">
-        <v>2261</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B373" t="s">
         <v>16</v>
@@ -21417,13 +21414,13 @@
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B374" t="s">
         <v>2263</v>
       </c>
-      <c r="B374" t="s">
+      <c r="C374" t="s">
         <v>2264</v>
-      </c>
-      <c r="C374" t="s">
-        <v>2265</v>
       </c>
       <c r="D374" t="s">
         <v>624</v>
@@ -21432,13 +21429,13 @@
         <v>16</v>
       </c>
       <c r="F374" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="G374" t="s">
+        <v>2246</v>
+      </c>
+      <c r="H374" t="s">
         <v>2247</v>
-      </c>
-      <c r="H374" t="s">
-        <v>2248</v>
       </c>
       <c r="I374" t="s">
         <v>1074</v>
@@ -21447,33 +21444,33 @@
         <v>32</v>
       </c>
       <c r="K374" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="L374" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="B375" t="s">
         <v>1401</v>
       </c>
       <c r="C375" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D375" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E375" t="s">
+        <v>16</v>
+      </c>
+      <c r="F375" t="s">
         <v>2269</v>
       </c>
-      <c r="D375" t="s">
-        <v>2246</v>
-      </c>
-      <c r="E375" t="s">
-        <v>16</v>
-      </c>
-      <c r="F375" t="s">
-        <v>2270</v>
-      </c>
       <c r="G375" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="H375" t="s">
         <v>115</v>
@@ -21488,30 +21485,30 @@
         <v>571</v>
       </c>
       <c r="L375" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="B376" t="s">
         <v>1401</v>
       </c>
       <c r="C376" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D376" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E376" t="s">
+        <v>16</v>
+      </c>
+      <c r="F376" t="s">
         <v>2269</v>
       </c>
-      <c r="D376" t="s">
-        <v>2246</v>
-      </c>
-      <c r="E376" t="s">
-        <v>16</v>
-      </c>
-      <c r="F376" t="s">
-        <v>2270</v>
-      </c>
       <c r="G376" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="H376" t="s">
         <v>115</v>
@@ -21523,36 +21520,36 @@
         <v>32</v>
       </c>
       <c r="K376" t="s">
+        <v>2272</v>
+      </c>
+      <c r="L376" t="s">
         <v>2273</v>
-      </c>
-      <c r="L376" t="s">
-        <v>2274</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B377" t="s">
+        <v>2243</v>
+      </c>
+      <c r="C377" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D377" t="s">
         <v>2275</v>
       </c>
-      <c r="B377" t="s">
-        <v>2244</v>
-      </c>
-      <c r="C377" t="s">
-        <v>2245</v>
-      </c>
-      <c r="D377" t="s">
+      <c r="E377" t="s">
+        <v>16</v>
+      </c>
+      <c r="F377" t="s">
         <v>2276</v>
       </c>
-      <c r="E377" t="s">
-        <v>16</v>
-      </c>
-      <c r="F377" t="s">
-        <v>2277</v>
-      </c>
       <c r="G377" t="s">
+        <v>2246</v>
+      </c>
+      <c r="H377" t="s">
         <v>2247</v>
-      </c>
-      <c r="H377" t="s">
-        <v>2248</v>
       </c>
       <c r="I377" t="s">
         <v>1074</v>
@@ -21561,10 +21558,10 @@
         <v>32</v>
       </c>
       <c r="K377" t="s">
-        <v>1680</v>
+        <v>16</v>
       </c>
       <c r="L377" t="s">
-        <v>1748</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
